--- a/data/datasets/features/cleaned_feature_group_3.xlsx
+++ b/data/datasets/features/cleaned_feature_group_3.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,39 +460,49 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>mean_vix[t]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>std_vix[t]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>federal_funds_rate[t]</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total_return_brent_price[t-1]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>std_return_brent_price[t-1]</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_return_usd_rub_price[t-1]</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>std_return_usd_rub_price[t-1]</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_vix[t-1]</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>std_vix[t-1]</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>federal_funds_rate[t-1]</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -514,14 +524,20 @@
         <v>0.007614114297173012</v>
       </c>
       <c r="G2" t="n">
+        <v>19.38904761904762</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.545965409580385</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -543,25 +559,31 @@
         <v>0.005175977838522479</v>
       </c>
       <c r="G3" t="n">
+        <v>24.95315789473684</v>
+      </c>
+      <c r="H3" t="n">
         <v>4.679108477087369</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J3" t="n">
         <v>-0.2083057247324582</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.0249717348231001</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.02092808777598254</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.007614114297173012</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>19.38904761904762</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.545965409580385</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -584,25 +606,31 @@
         <v>0.00767740207285164</v>
       </c>
       <c r="G4" t="n">
+        <v>19.57238095238095</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.052144986987775</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>-0.08696520787214412</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.03410594514884444</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.03204420368566119</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.005175977838522479</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
+        <v>24.95315789473684</v>
+      </c>
+      <c r="O4" t="n">
         <v>4.679108477087369</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.27</v>
       </c>
     </row>
     <row r="5">
@@ -625,25 +653,31 @@
         <v>0.003351028974462042</v>
       </c>
       <c r="G5" t="n">
+        <v>15.23473684210526</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.759066447252827</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.1227159600702667</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.01754860520314563</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>-0.05522857571044959</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.00767740207285164</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
+        <v>19.57238095238095</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.052144986987775</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -666,25 +700,31 @@
         <v>0.004996366521960061</v>
       </c>
       <c r="G6" t="n">
+        <v>14.4852380952381</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.16015352021885</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.079414259041096</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.01400238897225686</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.004762711318739399</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.003351028974462042</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>15.23473684210526</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.759066447252827</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -707,25 +747,31 @@
         <v>0.003295479220250773</v>
       </c>
       <c r="G7" t="n">
+        <v>12.94904761904762</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.5938005116358928</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.01897987184784533</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.007850841427225962</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>-0.004097493053802914</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.004996366521960061</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
+        <v>14.4852380952381</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.16015352021885</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.41</v>
       </c>
     </row>
     <row r="8">
@@ -748,25 +794,31 @@
         <v>0.00386377469909763</v>
       </c>
       <c r="G8" t="n">
+        <v>16.72181818181818</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.938923698402056</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.05906464747060003</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.01317376988165363</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>-0.01562532991270782</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.003295479220250773</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
+        <v>12.94904761904762</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.5938005116358928</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.42</v>
       </c>
     </row>
     <row r="9">
@@ -789,25 +841,31 @@
         <v>0.004701030694405237</v>
       </c>
       <c r="G9" t="n">
+        <v>15.836</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.9362152249180838</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J9" t="n">
         <v>-0.148676806160287</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.01929815624022268</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.01250290520727493</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.00386377469909763</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
+        <v>16.72181818181818</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.938923698402056</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.39</v>
       </c>
     </row>
     <row r="10">
@@ -830,25 +888,31 @@
         <v>0.003434803494771856</v>
       </c>
       <c r="G10" t="n">
+        <v>13.30590909090909</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.925432506817934</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.04418421157613039</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.01863300489993277</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>-0.03739508006281955</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.004701030694405237</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
+        <v>15.836</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.9362152249180838</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.38</v>
       </c>
     </row>
     <row r="11">
@@ -871,25 +935,31 @@
         <v>0.006943986128889881</v>
       </c>
       <c r="G11" t="n">
+        <v>18.97909090909091</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.058741892957488</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J11" t="n">
         <v>-0.005125428631282958</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.0172624009387849</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.009162039756814622</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.003434803494771856</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
+        <v>13.30590909090909</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.925432506817934</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -912,25 +982,31 @@
         <v>0.00475185312873279</v>
       </c>
       <c r="G12" t="n">
+        <v>15.559</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.455331034868916</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J12" t="n">
         <v>-0.08545544078028744</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.02073882698898222</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.0480357276018859</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.006943986128889881</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
+        <v>18.97909090909091</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.058741892957488</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.13</v>
       </c>
     </row>
     <row r="13">
@@ -953,25 +1029,31 @@
         <v>0.003917676452437225</v>
       </c>
       <c r="G13" t="n">
+        <v>15.46652173913044</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.599121545123296</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.007939901497488577</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.03440981350426479</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>-0.02806965402462236</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.00475185312873279</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
+        <v>15.559</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.455331034868916</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.04</v>
       </c>
     </row>
     <row r="14">
@@ -994,25 +1076,31 @@
         <v>0.003763294442291152</v>
       </c>
       <c r="G14" t="n">
+        <v>12.5235</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.4645912181692639</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.001177163173014861</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.01355618893658511</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>-0.0110088699490154</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.003917676452437225</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
+        <v>15.46652173913044</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.599121545123296</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.83</v>
       </c>
     </row>
     <row r="15">
@@ -1035,25 +1123,31 @@
         <v>0.00308157069417122</v>
       </c>
       <c r="G15" t="n">
+        <v>13.75666666666667</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.285750105321144</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.02046149735789982</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.0177647053565</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.003756660884749685</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.003763294442291152</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
+        <v>12.5235</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.4645912181692639</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="16">
@@ -1076,25 +1170,31 @@
         <v>0.005849016391496313</v>
       </c>
       <c r="G16" t="n">
+        <v>13.94095238095238</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.993732441331848</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.08367137429699589</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.008621228703764097</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>-0.03885672658973238</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.00308157069417122</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
+        <v>13.75666666666667</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.285750105321144</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="17">
@@ -1117,25 +1217,31 @@
         <v>0.006980535088408272</v>
       </c>
       <c r="G17" t="n">
+        <v>19.62894736842105</v>
+      </c>
+      <c r="H17" t="n">
         <v>8.332956587975003</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J17" t="n">
         <v>-0.1530406898041097</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.01803824118979518</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.03345627719151167</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.005849016391496313</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
+        <v>13.94095238095238</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.993732441331848</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="18">
@@ -1158,25 +1264,31 @@
         <v>0.02474953451846196</v>
       </c>
       <c r="G18" t="n">
+        <v>57.73681818181819</v>
+      </c>
+      <c r="H18" t="n">
         <v>14.56076246903485</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J18" t="n">
         <v>-0.1232471070328449</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.02383399149480493</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.04138508948691833</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.006980535088408272</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
+        <v>19.62894736842105</v>
+      </c>
+      <c r="O18" t="n">
         <v>8.332956587975003</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.58</v>
       </c>
     </row>
     <row r="19">
@@ -1199,25 +1311,31 @@
         <v>0.01233713413879717</v>
       </c>
       <c r="G19" t="n">
+        <v>41.45380952380953</v>
+      </c>
+      <c r="H19" t="n">
         <v>6.215479447468613</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J19" t="n">
         <v>-0.6588065158854515</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.09244367625428587</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.1609662611095271</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.02474953451846196</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
+        <v>57.73681818181819</v>
+      </c>
+      <c r="O19" t="n">
         <v>14.56076246903485</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.65</v>
       </c>
     </row>
     <row r="20">
@@ -1240,25 +1358,31 @@
         <v>0.007779517349259741</v>
       </c>
       <c r="G20" t="n">
+        <v>30.897</v>
+      </c>
+      <c r="H20" t="n">
         <v>3.137587239298775</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.02814944326648883</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.1022861364849053</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>-0.05282178653956215</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.01233713413879717</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
+        <v>41.45380952380953</v>
+      </c>
+      <c r="O20" t="n">
         <v>6.215479447468613</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.05</v>
       </c>
     </row>
     <row r="21">
@@ -1281,25 +1405,31 @@
         <v>0.008252839500907329</v>
       </c>
       <c r="G21" t="n">
+        <v>31.11954545454546</v>
+      </c>
+      <c r="H21" t="n">
         <v>4.168944684635403</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.3441056577316823</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.04933314957947674</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>-0.05561893834922671</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.007779517349259741</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
+        <v>30.897</v>
+      </c>
+      <c r="O21" t="n">
         <v>3.137587239298775</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.05</v>
       </c>
     </row>
     <row r="22">
@@ -1322,25 +1452,31 @@
         <v>0.006926419924566616</v>
       </c>
       <c r="G22" t="n">
+        <v>26.84045454545454</v>
+      </c>
+      <c r="H22" t="n">
         <v>2.184271649931079</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.1015510887246389</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.02919175005928907</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.001476673730918421</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.008252839500907329</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
+        <v>31.11954545454546</v>
+      </c>
+      <c r="O22" t="n">
         <v>4.168944684635403</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="23">
@@ -1363,25 +1499,31 @@
         <v>0.00776015707211131</v>
       </c>
       <c r="G23" t="n">
+        <v>22.88952380952381</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.169348007183817</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.0487558476683394</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.0133773897411011</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.05508625334978667</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.006926419924566616</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
+        <v>26.84045454545454</v>
+      </c>
+      <c r="O23" t="n">
         <v>2.184271649931079</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="24">
@@ -1404,25 +1546,31 @@
         <v>0.008798906163590775</v>
       </c>
       <c r="G24" t="n">
+        <v>27.64761904761905</v>
+      </c>
+      <c r="H24" t="n">
         <v>2.162988452955553</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J24" t="n">
         <v>0.04167269640056803</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.01243894957924537</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>-0.005832806738951923</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.00776015707211131</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
+        <v>22.88952380952381</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.169348007183817</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="25">
@@ -1445,25 +1593,31 @@
         <v>0.007850991309756561</v>
       </c>
       <c r="G25" t="n">
+        <v>29.43863636363636</v>
+      </c>
+      <c r="H25" t="n">
         <v>4.264979534874752</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J25" t="n">
         <v>-0.07872691801001652</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.02414057805820564</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.04648166892383809</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.008798906163590775</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
+        <v>27.64761904761905</v>
+      </c>
+      <c r="O25" t="n">
         <v>2.162988452955553</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="26">
@@ -1486,25 +1640,31 @@
         <v>0.008404160434145207</v>
       </c>
       <c r="G26" t="n">
+        <v>24.9955</v>
+      </c>
+      <c r="H26" t="n">
         <v>4.465363160807275</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J26" t="n">
         <v>-0.1066275414845981</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.02628358974594609</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0243529227940904</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.007850991309756561</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
+        <v>29.43863636363636</v>
+      </c>
+      <c r="O26" t="n">
         <v>4.264979534874752</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="27">
@@ -1527,25 +1687,31 @@
         <v>0.008748920080177925</v>
       </c>
       <c r="G27" t="n">
+        <v>22.37409090909091</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.259911784859442</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J27" t="n">
         <v>0.2291476774252508</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.02403538231273612</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>-0.03841103765353981</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.008404160434145207</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
+        <v>24.9955</v>
+      </c>
+      <c r="O27" t="n">
         <v>4.465363160807275</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="28">
@@ -1568,25 +1734,31 @@
         <v>0.006862156521610678</v>
       </c>
       <c r="G28" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="H28" t="n">
         <v>4.244426410665587</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J28" t="n">
         <v>0.08280173069722929</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.01799601257905896</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>-0.03485594873478348</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.008748920080177925</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
+        <v>22.37409090909091</v>
+      </c>
+      <c r="O28" t="n">
         <v>1.259911784859442</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="29">
@@ -1609,25 +1781,31 @@
         <v>0.006064799251721781</v>
       </c>
       <c r="G29" t="n">
+        <v>23.14052631578948</v>
+      </c>
+      <c r="H29" t="n">
         <v>2.894831550816444</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.0633051622552121</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.01962982310066791</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.02578017464928628</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.006862156521610678</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="O29" t="n">
         <v>4.244426410665587</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="30">
@@ -1650,25 +1828,31 @@
         <v>0.006382323481874727</v>
       </c>
       <c r="G30" t="n">
+        <v>21.84304347826087</v>
+      </c>
+      <c r="H30" t="n">
         <v>2.659558122529875</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.1562744277441839</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.01871592486662461</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>-0.01871730219077516</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.006064799251721781</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
+        <v>23.14052631578948</v>
+      </c>
+      <c r="O30" t="n">
         <v>2.894831550816444</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="31">
@@ -1691,25 +1875,31 @@
         <v>0.00655127875650176</v>
       </c>
       <c r="G31" t="n">
+        <v>17.41619047619048</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.689619287654256</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J31" t="n">
         <v>-0.0211789232274926</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.03195698302128104</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.01859974922080898</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.006382323481874727</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
+        <v>21.84304347826087</v>
+      </c>
+      <c r="O31" t="n">
         <v>2.659558122529875</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1732,25 +1922,31 @@
         <v>0.00408480157134741</v>
       </c>
       <c r="G32" t="n">
+        <v>19.7605</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.59219978721589</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J32" t="n">
         <v>0.05205406406953372</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.01682936057936818</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>-0.006768679566598657</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.00655127875650176</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
+        <v>17.41619047619048</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.689619287654256</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1773,25 +1969,31 @@
         <v>0.004333663636067009</v>
       </c>
       <c r="G33" t="n">
+        <v>16.95681818181818</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.201845352398658</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J33" t="n">
         <v>0.04445176257083361</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.01714843167272181</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>-0.02434325065433818</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.00408480157134741</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
+        <v>19.7605</v>
+      </c>
+      <c r="O33" t="n">
         <v>2.59219978721589</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.06</v>
       </c>
     </row>
     <row r="34">
@@ -1814,25 +2016,31 @@
         <v>0.005187007161045468</v>
       </c>
       <c r="G34" t="n">
+        <v>17.60333333333334</v>
+      </c>
+      <c r="H34" t="n">
         <v>1.672851856361864</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J34" t="n">
         <v>0.07232735773168297</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.01008695610812465</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>-0.006301579839402827</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.004333663636067009</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
+        <v>16.95681818181818</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.201845352398658</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="35">
@@ -1855,25 +2063,31 @@
         <v>0.003948171112446263</v>
       </c>
       <c r="G35" t="n">
+        <v>17.47272727272727</v>
+      </c>
+      <c r="H35" t="n">
         <v>1.702721020736772</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J35" t="n">
         <v>0.007338747994579897</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.02249451638050532</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.002290110794674227</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.005187007161045468</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
+        <v>17.60333333333334</v>
+      </c>
+      <c r="O35" t="n">
         <v>1.672851856361864</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1896,25 +2110,31 @@
         <v>0.004159316182393658</v>
       </c>
       <c r="G36" t="n">
+        <v>19.8247619047619</v>
+      </c>
+      <c r="H36" t="n">
         <v>2.687224625980531</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J36" t="n">
         <v>-0.0479264054366153</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.02147557901369431</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.003657120089076038</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.003948171112446263</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
+        <v>17.47272727272727</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.702721020736772</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="37">
@@ -1937,25 +2157,31 @@
         <v>0.006152558647489772</v>
       </c>
       <c r="G37" t="n">
+        <v>17.87142857142857</v>
+      </c>
+      <c r="H37" t="n">
         <v>2.418380213519548</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J37" t="n">
         <v>0.08882284547076491</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.01236359034660816</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>-0.006870510278375264</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.004159316182393658</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
+        <v>19.8247619047619</v>
+      </c>
+      <c r="O37" t="n">
         <v>2.687224625980531</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="38">
@@ -1978,25 +2204,31 @@
         <v>0.008267092521546561</v>
       </c>
       <c r="G38" t="n">
+        <v>18.50047619047619</v>
+      </c>
+      <c r="H38" t="n">
         <v>3.563772546320089</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J38" t="n">
         <v>0.06389225569147516</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.01278420344083869</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>-0.03050645440731614</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.006152558647489772</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
+        <v>17.87142857142857</v>
+      </c>
+      <c r="O38" t="n">
         <v>2.418380213519548</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="39">
@@ -2019,25 +2251,31 @@
         <v>0.004298668248452551</v>
       </c>
       <c r="G39" t="n">
+        <v>21.35454545454546</v>
+      </c>
+      <c r="H39" t="n">
         <v>4.240051355565815</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J39" t="n">
         <v>-0.1604155242319534</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.02787388305943026</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.04854917478554643</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.008267092521546561</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
+        <v>18.50047619047619</v>
+      </c>
+      <c r="O39" t="n">
         <v>3.563772546320089</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="40">
@@ -2060,25 +2298,31 @@
         <v>0.009483030774534117</v>
       </c>
       <c r="G40" t="n">
+        <v>23.181</v>
+      </c>
+      <c r="H40" t="n">
         <v>5.229567658491172</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.09114897537470146</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.02030166632479417</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.01178973550234996</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.004298668248452551</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
+        <v>21.35454545454546</v>
+      </c>
+      <c r="O40" t="n">
         <v>4.240051355565815</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="41">
@@ -2101,25 +2345,31 @@
         <v>0.04806827251103409</v>
       </c>
       <c r="G41" t="n">
+        <v>25.74842105263158</v>
+      </c>
+      <c r="H41" t="n">
         <v>3.347284576352556</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J41" t="n">
         <v>0.1361741637852312</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>0.01253070743061918</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.0274619806588996</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>0.009483030774534117</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
+        <v>23.181</v>
+      </c>
+      <c r="O41" t="n">
         <v>5.229567658491172</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="42">
@@ -2142,25 +2392,31 @@
         <v>0.06943364048238529</v>
       </c>
       <c r="G42" t="n">
+        <v>26.96869565217391</v>
+      </c>
+      <c r="H42" t="n">
         <v>5.5189584856926</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J42" t="n">
         <v>0.09407775569449406</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>0.01670657178064555</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.3010570066041458</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.04806827251103409</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
+        <v>25.74842105263158</v>
+      </c>
+      <c r="O42" t="n">
         <v>3.347284576352556</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="43">
@@ -2183,25 +2439,31 @@
         <v>0.02321907593434514</v>
       </c>
       <c r="G43" t="n">
+        <v>24.3735</v>
+      </c>
+      <c r="H43" t="n">
         <v>4.61098947595507</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J43" t="n">
         <v>0.07394052467177747</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>0.06285626225120751</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>-0.2433458182037809</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>0.06943364048238529</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
+        <v>26.96869565217391</v>
+      </c>
+      <c r="O43" t="n">
         <v>5.5189584856926</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -2224,25 +2486,31 @@
         <v>0.0325070400424397</v>
       </c>
       <c r="G44" t="n">
+        <v>29.31363636363636</v>
+      </c>
+      <c r="H44" t="n">
         <v>2.58381693560321</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.004061782375486267</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>0.02745939557828022</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>-0.1464974294243371</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>0.02321907593434514</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
+        <v>24.3735</v>
+      </c>
+      <c r="O44" t="n">
         <v>4.61098947595507</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.33</v>
       </c>
     </row>
     <row r="45">
@@ -2265,25 +2533,31 @@
         <v>0.02250628963623971</v>
       </c>
       <c r="G45" t="n">
+        <v>28.23318181818182</v>
+      </c>
+      <c r="H45" t="n">
         <v>2.953261935657935</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J45" t="n">
         <v>0.09172154624296436</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>0.02744071340351742</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>-0.1298957594541044</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>0.0325070400424397</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
+        <v>29.31363636363636</v>
+      </c>
+      <c r="O45" t="n">
         <v>2.58381693560321</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.77</v>
       </c>
     </row>
     <row r="46">
@@ -2306,25 +2580,31 @@
         <v>0.03836206899597069</v>
       </c>
       <c r="G46" t="n">
+        <v>24.99523809523809</v>
+      </c>
+      <c r="H46" t="n">
         <v>1.844420285747312</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J46" t="n">
         <v>-0.06273400936971196</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>0.02073989683157592</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>-0.1335313926245227</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.02250628963623971</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
+        <v>28.23318181818182</v>
+      </c>
+      <c r="O46" t="n">
         <v>2.953261935657935</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.21</v>
       </c>
     </row>
     <row r="47">
@@ -2347,25 +2627,31 @@
         <v>0.01377709568572413</v>
       </c>
       <c r="G47" t="n">
+        <v>22.1695652173913</v>
+      </c>
+      <c r="H47" t="n">
         <v>2.268230143567826</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J47" t="n">
         <v>-0.04879016416943216</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>0.03482850855790699</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.1254341823919036</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>0.03836206899597069</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
+        <v>24.99523809523809</v>
+      </c>
+      <c r="O47" t="n">
         <v>1.844420285747312</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.68</v>
       </c>
     </row>
     <row r="48">
@@ -2388,25 +2674,31 @@
         <v>0.02232706275012171</v>
       </c>
       <c r="G48" t="n">
+        <v>27.34181818181818</v>
+      </c>
+      <c r="H48" t="n">
         <v>2.881455710745355</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J48" t="n">
         <v>-0.0909351488399599</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>0.02638733026231814</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>-0.04149973090675285</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>0.01377709568572413</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
+        <v>22.1695652173913</v>
+      </c>
+      <c r="O48" t="n">
         <v>2.268230143567826</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.33</v>
       </c>
     </row>
     <row r="49">
@@ -2429,25 +2721,31 @@
         <v>0.01785084562105857</v>
       </c>
       <c r="G49" t="n">
+        <v>30.00571428571429</v>
+      </c>
+      <c r="H49" t="n">
         <v>2.228312301784854</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J49" t="n">
         <v>-0.1041209958714493</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>0.02738767077377121</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.003384097984240775</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>0.02232706275012171</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
+        <v>27.34181818181818</v>
+      </c>
+      <c r="O49" t="n">
         <v>2.881455710745355</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.56</v>
       </c>
     </row>
     <row r="50">
@@ -2470,25 +2768,31 @@
         <v>0.0120192778730323</v>
       </c>
       <c r="G50" t="n">
+        <v>23.29909090909091</v>
+      </c>
+      <c r="H50" t="n">
         <v>1.903940548018665</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="J50" t="n">
         <v>0.08165053336875161</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>0.0205899249517067</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.02995232228335087</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.01785084562105857</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
+        <v>30.00571428571429</v>
+      </c>
+      <c r="O50" t="n">
         <v>2.228312301784854</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.08</v>
       </c>
     </row>
     <row r="51">
@@ -2511,25 +2815,31 @@
         <v>0.02147359623017822</v>
       </c>
       <c r="G51" t="n">
+        <v>21.78428571428572</v>
+      </c>
+      <c r="H51" t="n">
         <v>1.270596597778271</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J51" t="n">
         <v>-0.06922368510597998</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>0.02256495942543172</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>-0.001230264662041236</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.0120192778730323</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
+        <v>23.29909090909091</v>
+      </c>
+      <c r="O51" t="n">
         <v>1.903940548018665</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.78</v>
       </c>
     </row>
     <row r="52">
@@ -2552,25 +2862,31 @@
         <v>0.01730537926236181</v>
       </c>
       <c r="G52" t="n">
+        <v>20.16904761904762</v>
+      </c>
+      <c r="H52" t="n">
         <v>1.33177665080112</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J52" t="n">
         <v>-0.007530592269930025</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>0.02262950786837145</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>0.1739429623493587</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.02147359623017822</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
+        <v>21.78428571428572</v>
+      </c>
+      <c r="O52" t="n">
         <v>1.270596597778271</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4.1</v>
       </c>
     </row>
     <row r="53">
@@ -2593,25 +2909,31 @@
         <v>0.01220240696239372</v>
       </c>
       <c r="G53" t="n">
+        <v>20.1205</v>
+      </c>
+      <c r="H53" t="n">
         <v>1.388514825651004</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="J53" t="n">
         <v>-0.00536381883011483</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>0.0226579202348202</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>-0.04767010201813004</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>0.01730537926236181</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
+        <v>20.16904761904762</v>
+      </c>
+      <c r="O53" t="n">
         <v>1.33177665080112</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="54">
@@ -2634,25 +2956,31 @@
         <v>0.009022527595862667</v>
       </c>
       <c r="G54" t="n">
+        <v>21.64434782608696</v>
+      </c>
+      <c r="H54" t="n">
         <v>2.563934877358621</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J54" t="n">
         <v>-0.0287021600277555</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>0.01821455484382534</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.08215681578640766</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>0.01220240696239372</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
+        <v>20.1205</v>
+      </c>
+      <c r="O54" t="n">
         <v>1.388514825651004</v>
-      </c>
-      <c r="M54" t="n">
-        <v>4.57</v>
       </c>
     </row>
     <row r="55">
@@ -2675,25 +3003,31 @@
         <v>0.01007252320863631</v>
       </c>
       <c r="G55" t="n">
+        <v>17.81789473684211</v>
+      </c>
+      <c r="H55" t="n">
         <v>1.097272269196913</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="J55" t="n">
         <v>-0.03901377992700716</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>0.02177356950536968</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>0.03832781140600261</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.009022527595862667</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
+        <v>21.64434782608696</v>
+      </c>
+      <c r="O55" t="n">
         <v>2.563934877358621</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.65</v>
       </c>
     </row>
     <row r="56">
@@ -2716,25 +3050,31 @@
         <v>0.02442085879213558</v>
       </c>
       <c r="G56" t="n">
+        <v>17.63608695652174</v>
+      </c>
+      <c r="H56" t="n">
         <v>1.051996971696449</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.005116377293208352</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>0.02203274245491877</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.02501285998421832</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>0.01007252320863631</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
+        <v>17.81789473684211</v>
+      </c>
+      <c r="O56" t="n">
         <v>1.097272269196913</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.83</v>
       </c>
     </row>
     <row r="57">
@@ -2757,25 +3097,31 @@
         <v>0.01360008271698119</v>
       </c>
       <c r="G57" t="n">
+        <v>14.00318181818182</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.6424238799721272</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="J57" t="n">
         <v>-0.1077975824155546</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>0.02343299304381977</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0.01978644078042979</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>0.02442085879213558</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
+        <v>17.63608695652174</v>
+      </c>
+      <c r="O57" t="n">
         <v>1.051996971696449</v>
-      </c>
-      <c r="M57" t="n">
-        <v>5.06</v>
       </c>
     </row>
     <row r="58">
@@ -2798,25 +3144,31 @@
         <v>0.007930037888743073</v>
       </c>
       <c r="G58" t="n">
+        <v>13.93238095238095</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.6340102898368821</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.04154819687435474</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>0.01964487791635376</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.08518626219856706</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0.01360008271698119</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
+        <v>14.00318181818182</v>
+      </c>
+      <c r="O58" t="n">
         <v>0.6424238799721272</v>
-      </c>
-      <c r="M58" t="n">
-        <v>5.08</v>
       </c>
     </row>
     <row r="59">
@@ -2839,25 +3191,31 @@
         <v>0.0139509380198123</v>
       </c>
       <c r="G59" t="n">
+        <v>15.85391304347826</v>
+      </c>
+      <c r="H59" t="n">
         <v>1.193248961032001</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J59" t="n">
         <v>0.1265078491585578</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>0.0122209185216263</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>0.031545587880494</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>0.007930037888743073</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
+        <v>13.93238095238095</v>
+      </c>
+      <c r="O59" t="n">
         <v>0.6340102898368821</v>
-      </c>
-      <c r="M59" t="n">
-        <v>5.12</v>
       </c>
     </row>
     <row r="60">
@@ -2880,25 +3238,31 @@
         <v>0.01303114148627787</v>
       </c>
       <c r="G60" t="n">
+        <v>15.17333333333333</v>
+      </c>
+      <c r="H60" t="n">
         <v>1.90248346466752</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.01731091732295376</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
         <v>0.01217535515673995</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>0.0450504383641892</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>0.0139509380198123</v>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
+        <v>15.85391304347826</v>
+      </c>
+      <c r="O60" t="n">
         <v>1.193248961032001</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="61">
@@ -2921,25 +3285,31 @@
         <v>0.01414067154402368</v>
       </c>
       <c r="G61" t="n">
+        <v>18.88772727272727</v>
+      </c>
+      <c r="H61" t="n">
         <v>1.614841675324128</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.06109878340603814</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>0.01329274333000474</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>0.006355129702409812</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>0.01303114148627787</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
+        <v>15.17333333333333</v>
+      </c>
+      <c r="O61" t="n">
         <v>1.90248346466752</v>
-      </c>
-      <c r="M61" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="62">
@@ -2962,25 +3332,31 @@
         <v>0.008443310652633072</v>
       </c>
       <c r="G62" t="n">
+        <v>14.01909090909091</v>
+      </c>
+      <c r="H62" t="n">
         <v>1.143886062803164</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J62" t="n">
         <v>-0.07501689256068556</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>0.02555183869610684</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>-0.03332586225993417</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>0.01414067154402368</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
+        <v>18.88772727272727</v>
+      </c>
+      <c r="O62" t="n">
         <v>1.614841675324128</v>
-      </c>
-      <c r="M62" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="63">
@@ -3003,25 +3379,31 @@
         <v>0.01052001119842303</v>
       </c>
       <c r="G63" t="n">
+        <v>12.7185</v>
+      </c>
+      <c r="H63" t="n">
         <v>0.4382894381330075</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J63" t="n">
         <v>-0.06352680853327897</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>0.02197966959676846</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>-0.03535818525319012</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>0.008443310652633072</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
+        <v>14.01909090909091</v>
+      </c>
+      <c r="O63" t="n">
         <v>1.143886062803164</v>
-      </c>
-      <c r="M63" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="64">
@@ -3044,25 +3426,31 @@
         <v>0.007723347359243268</v>
       </c>
       <c r="G64" t="n">
+        <v>13.38863636363636</v>
+      </c>
+      <c r="H64" t="n">
         <v>0.6136486931581607</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J64" t="n">
         <v>-0.04154824863735573</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>0.01823027649878998</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>-0.008081324947482926</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>0.01052001119842303</v>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
+        <v>12.7185</v>
+      </c>
+      <c r="O64" t="n">
         <v>0.4382894381330075</v>
-      </c>
-      <c r="M64" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="65">
@@ -3085,25 +3473,31 @@
         <v>0.007827277167906835</v>
       </c>
       <c r="G65" t="n">
+        <v>13.98047619047619</v>
+      </c>
+      <c r="H65" t="n">
         <v>0.8389605246403211</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J65" t="n">
         <v>0.0457708083142494</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>0.01554357592729482</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>0.006821594922961971</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
         <v>0.007723347359243268</v>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
+        <v>13.38863636363636</v>
+      </c>
+      <c r="O65" t="n">
         <v>0.6136486931581607</v>
-      </c>
-      <c r="M65" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="66">
@@ -3126,25 +3520,31 @@
         <v>0.005727159813180832</v>
       </c>
       <c r="G66" t="n">
+        <v>13.7875</v>
+      </c>
+      <c r="H66" t="n">
         <v>0.7280679190411031</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J66" t="n">
         <v>0.01634846810349799</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>0.01356340470450881</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>0.01430430197597854</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>0.007827277167906835</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
+        <v>13.98047619047619</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.8389605246403211</v>
-      </c>
-      <c r="M66" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="67">
@@ -3167,25 +3567,31 @@
         <v>0.004741208912333881</v>
       </c>
       <c r="G67" t="n">
+        <v>16.13772727272728</v>
+      </c>
+      <c r="H67" t="n">
         <v>1.561763142270336</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J67" t="n">
         <v>0.05974927287661114</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>0.01053552499573359</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>0.002094044453324173</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>0.005727159813180832</v>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
+        <v>13.7875</v>
+      </c>
+      <c r="O67" t="n">
         <v>0.7280679190411031</v>
-      </c>
-      <c r="M67" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="68">
@@ -3208,25 +3614,31 @@
         <v>0.008691565081202765</v>
       </c>
       <c r="G68" t="n">
+        <v>13.05869565217391</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.9397306400715727</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J68" t="n">
         <v>-0.01329576207996919</v>
       </c>
-      <c r="I68" t="n">
+      <c r="K68" t="n">
         <v>0.01260965402832862</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>0.0217272526446779</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>0.004741208912333881</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
+        <v>16.13772727272728</v>
+      </c>
+      <c r="O68" t="n">
         <v>1.561763142270336</v>
-      </c>
-      <c r="M68" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="69">
@@ -3249,25 +3661,31 @@
         <v>0.01775820860383106</v>
       </c>
       <c r="G69" t="n">
+        <v>12.667</v>
+      </c>
+      <c r="H69" t="n">
         <v>0.4079486551799842</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J69" t="n">
         <v>-0.05440997605198916</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>0.01152375881011632</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>-0.03348887845206772</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>0.008691565081202765</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
+        <v>13.05869565217391</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.9397306400715727</v>
-      </c>
-      <c r="M69" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="70">
@@ -3290,25 +3708,31 @@
         <v>0.009564617488582266</v>
       </c>
       <c r="G70" t="n">
+        <v>14.37391304347826</v>
+      </c>
+      <c r="H70" t="n">
         <v>2.16911112739849</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J70" t="n">
         <v>0.04176047498791657</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>0.01614362447475471</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>-0.0470589927093199</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>0.01775820860383106</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
+        <v>12.667</v>
+      </c>
+      <c r="O70" t="n">
         <v>0.4079486551799842</v>
-      </c>
-      <c r="M70" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="71">
@@ -3331,25 +3755,31 @@
         <v>0.009761818692462855</v>
       </c>
       <c r="G71" t="n">
+        <v>19.31227272727273</v>
+      </c>
+      <c r="H71" t="n">
         <v>5.865430550362484</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J71" t="n">
         <v>-0.04040953833787686</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>0.01416325562485151</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>-0.01433697055372551</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
         <v>0.009564617488582266</v>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
+        <v>14.37391304347826</v>
+      </c>
+      <c r="O71" t="n">
         <v>2.16911112739849</v>
-      </c>
-      <c r="M71" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="72">
@@ -3372,25 +3802,31 @@
         <v>0.0118997720702875</v>
       </c>
       <c r="G72" t="n">
+        <v>17.66333333333333</v>
+      </c>
+      <c r="H72" t="n">
         <v>2.072204944819246</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J72" t="n">
         <v>-0.05590302959248028</v>
       </c>
-      <c r="I72" t="n">
+      <c r="K72" t="n">
         <v>0.0207464713571433</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>0.06188599207172185</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
         <v>0.009761818692462855</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
+        <v>19.31227272727273</v>
+      </c>
+      <c r="O72" t="n">
         <v>5.865430550362484</v>
-      </c>
-      <c r="M72" t="n">
-        <v>5.33</v>
       </c>
     </row>
     <row r="73">
@@ -3413,25 +3849,31 @@
         <v>0.009354838820650968</v>
       </c>
       <c r="G73" t="n">
+        <v>19.96086956521739</v>
+      </c>
+      <c r="H73" t="n">
         <v>1.292481450696782</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="J73" t="n">
         <v>-0.06778844275006968</v>
       </c>
-      <c r="I73" t="n">
+      <c r="K73" t="n">
         <v>0.01894060332719271</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>0.026475279961792</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>0.0118997720702875</v>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
+        <v>17.66333333333333</v>
+      </c>
+      <c r="O73" t="n">
         <v>2.072204944819246</v>
-      </c>
-      <c r="M73" t="n">
-        <v>5.13</v>
       </c>
     </row>
     <row r="74">
@@ -3454,25 +3896,31 @@
         <v>0.02011459125433771</v>
       </c>
       <c r="G74" t="n">
+        <v>16.0152380952381</v>
+      </c>
+      <c r="H74" t="n">
         <v>2.496164295569545</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J74" t="n">
         <v>0.02820945646941109</v>
       </c>
-      <c r="I74" t="n">
+      <c r="K74" t="n">
         <v>0.02586154104174577</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>0.04763814262930577</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>0.009354838820650968</v>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
+        <v>19.96086956521739</v>
+      </c>
+      <c r="O74" t="n">
         <v>1.292481450696782</v>
-      </c>
-      <c r="M74" t="n">
-        <v>4.83</v>
       </c>
     </row>
     <row r="75">
@@ -3495,25 +3943,31 @@
         <v>0.01896100151695067</v>
       </c>
       <c r="G75" t="n">
+        <v>15.86619047619048</v>
+      </c>
+      <c r="H75" t="n">
         <v>3.710244569014928</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J75" t="n">
         <v>-0.02696023706897943</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>0.01620729811522459</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>0.08952111330537793</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>0.02011459125433771</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
+        <v>16.0152380952381</v>
+      </c>
+      <c r="O75" t="n">
         <v>2.496164295569545</v>
-      </c>
-      <c r="M75" t="n">
-        <v>4.64</v>
       </c>
     </row>
     <row r="76">
@@ -3536,25 +3990,31 @@
         <v>0.01354882412176747</v>
       </c>
       <c r="G76" t="n">
+        <v>16.76363636363637</v>
+      </c>
+      <c r="H76" t="n">
         <v>1.382604669092242</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J76" t="n">
         <v>0.03730353567577982</v>
       </c>
-      <c r="I76" t="n">
+      <c r="K76" t="n">
         <v>0.01071515564123842</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>0.02983103549145572</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
         <v>0.01896100151695067</v>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
+        <v>15.86619047619048</v>
+      </c>
+      <c r="O76" t="n">
         <v>3.710244569014928</v>
-      </c>
-      <c r="M76" t="n">
-        <v>4.48</v>
       </c>
     </row>
     <row r="77">
@@ -3577,25 +4037,31 @@
         <v>0.01528002373094152</v>
       </c>
       <c r="G77" t="n">
+        <v>16.968</v>
+      </c>
+      <c r="H77" t="n">
         <v>1.90090172508235</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J77" t="n">
         <v>0.0220718667402231</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>0.01386601990736324</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>-0.1066412914316999</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>0.01354882412176747</v>
       </c>
-      <c r="L77" t="n">
+      <c r="N77" t="n">
+        <v>16.76363636363637</v>
+      </c>
+      <c r="O77" t="n">
         <v>1.382604669092242</v>
-      </c>
-      <c r="M77" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="78">
@@ -3618,25 +4084,31 @@
         <v>0.01296875741207315</v>
       </c>
       <c r="G78" t="n">
+        <v>21.84142857142857</v>
+      </c>
+      <c r="H78" t="n">
         <v>2.921162928893707</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J78" t="n">
         <v>-0.04573600932268373</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>0.01429979251243517</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>-0.1013051790599331</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
         <v>0.01528002373094152</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
+        <v>16.968</v>
+      </c>
+      <c r="O78" t="n">
         <v>1.90090172508235</v>
-      </c>
-      <c r="M78" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="79">
@@ -3659,25 +4131,31 @@
         <v>0.01117936430274632</v>
       </c>
       <c r="G79" t="n">
+        <v>31.96619047619047</v>
+      </c>
+      <c r="H79" t="n">
         <v>8.411472805751959</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J79" t="n">
         <v>0.02205922047790398</v>
       </c>
-      <c r="I79" t="n">
+      <c r="K79" t="n">
         <v>0.01298494676068108</v>
       </c>
-      <c r="J79" t="n">
+      <c r="L79" t="n">
         <v>-0.07121613854999875</v>
       </c>
-      <c r="K79" t="n">
+      <c r="M79" t="n">
         <v>0.01296875741207315</v>
       </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
+        <v>21.84142857142857</v>
+      </c>
+      <c r="O79" t="n">
         <v>2.921162928893707</v>
-      </c>
-      <c r="M79" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="80">
@@ -3700,25 +4178,31 @@
         <v>0.01235307573875027</v>
       </c>
       <c r="G80" t="n">
+        <v>20.46227272727273</v>
+      </c>
+      <c r="H80" t="n">
         <v>2.387363422806447</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J80" t="n">
         <v>-0.2020845650115088</v>
       </c>
-      <c r="I80" t="n">
+      <c r="K80" t="n">
         <v>0.0300512695638949</v>
       </c>
-      <c r="J80" t="n">
+      <c r="L80" t="n">
         <v>-0.01222767123805291</v>
       </c>
-      <c r="K80" t="n">
+      <c r="M80" t="n">
         <v>0.01117936430274632</v>
       </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
+        <v>31.96619047619047</v>
+      </c>
+      <c r="O80" t="n">
         <v>8.411472805751959</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="81">
@@ -3741,25 +4225,31 @@
         <v>0.009364983025178771</v>
       </c>
       <c r="G81" t="n">
+        <v>18.40333333333334</v>
+      </c>
+      <c r="H81" t="n">
         <v>1.783517124485586</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J81" t="n">
         <v>0.02539562278101748</v>
       </c>
-      <c r="I81" t="n">
+      <c r="K81" t="n">
         <v>0.01708839537575698</v>
       </c>
-      <c r="J81" t="n">
+      <c r="L81" t="n">
         <v>-0.05793233794164809</v>
       </c>
-      <c r="K81" t="n">
+      <c r="M81" t="n">
         <v>0.01235307573875027</v>
       </c>
-      <c r="L81" t="n">
+      <c r="N81" t="n">
+        <v>20.46227272727273</v>
+      </c>
+      <c r="O81" t="n">
         <v>2.387363422806447</v>
-      </c>
-      <c r="M81" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="82">
@@ -3782,25 +4272,31 @@
         <v>0.006130916763870757</v>
       </c>
       <c r="G82" t="n">
+        <v>16.38130434782608</v>
+      </c>
+      <c r="H82" t="n">
         <v>0.7864321293482008</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J82" t="n">
         <v>0.06222991681722689</v>
       </c>
-      <c r="I82" t="n">
+      <c r="K82" t="n">
         <v>0.03690242265826561</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>0.01058161957614434</v>
       </c>
-      <c r="K82" t="n">
+      <c r="M82" t="n">
         <v>0.009364983025178771</v>
       </c>
-      <c r="L82" t="n">
+      <c r="N82" t="n">
+        <v>18.40333333333334</v>
+      </c>
+      <c r="O82" t="n">
         <v>1.783517124485586</v>
-      </c>
-      <c r="M82" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="83">
@@ -3823,25 +4319,31 @@
         <v>0.00487118981363292</v>
       </c>
       <c r="G83" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="H83" t="n">
         <v>1.479739841999261</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J83" t="n">
         <v>0.07445095914501554</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>0.01583689358054902</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>0.0362933337952196</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>0.006130916763870757</v>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
+        <v>16.38130434782608</v>
+      </c>
+      <c r="O83" t="n">
         <v>0.7864321293482008</v>
-      </c>
-      <c r="M83" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="84">
@@ -3864,25 +4366,31 @@
         <v>0.007829431898778709</v>
       </c>
       <c r="G84" t="n">
+        <v>15.78909090909091</v>
+      </c>
+      <c r="H84" t="n">
         <v>0.6662110997553479</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="J84" t="n">
         <v>-0.06207105608595676</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>0.01292258969452455</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>-0.01632851221181664</v>
       </c>
-      <c r="K84" t="n">
+      <c r="M84" t="n">
         <v>0.00487118981363292</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O84" t="n">
         <v>1.479739841999261</v>
-      </c>
-      <c r="M84" t="n">
-        <v>4.33</v>
       </c>
     </row>
     <row r="85">
@@ -3905,25 +4413,31 @@
         <v>0.008893129988024773</v>
       </c>
       <c r="G85" t="n">
+        <v>18.08652173913044</v>
+      </c>
+      <c r="H85" t="n">
         <v>2.327237161598299</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="J85" t="n">
         <v>-0.01960993907253972</v>
       </c>
-      <c r="I85" t="n">
+      <c r="K85" t="n">
         <v>0.01515331015804167</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>0.03838146321978009</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>0.007829431898778709</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
+        <v>15.78909090909091</v>
+      </c>
+      <c r="O85" t="n">
         <v>0.6662110997553479</v>
-      </c>
-      <c r="M85" t="n">
-        <v>4.22</v>
       </c>
     </row>
     <row r="86">
@@ -3946,25 +4460,31 @@
         <v>0.005079693070878803</v>
       </c>
       <c r="G86" t="n">
+        <v>19.7695</v>
+      </c>
+      <c r="H86" t="n">
         <v>2.881650614345517</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="J86" t="n">
         <v>-0.02402012523083563</v>
       </c>
-      <c r="I86" t="n">
+      <c r="K86" t="n">
         <v>0.01877918001656862</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>-0.02716289744606204</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
         <v>0.008893129988024773</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
+        <v>18.08652173913044</v>
+      </c>
+      <c r="O86" t="n">
         <v>2.327237161598299</v>
-      </c>
-      <c r="M86" t="n">
-        <v>4.09</v>
       </c>
     </row>
     <row r="87">
@@ -3987,25 +4507,31 @@
         <v>0.01092921516824441</v>
       </c>
       <c r="G87" t="n">
+        <v>15.54818181818182</v>
+      </c>
+      <c r="H87" t="n">
         <v>1.245363348637604</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J87" t="n">
         <v>-0.0356223637676365</v>
       </c>
-      <c r="I87" t="n">
+      <c r="K87" t="n">
         <v>0.01388730428625535</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>-0.0387324530719777</v>
       </c>
-      <c r="K87" t="n">
+      <c r="M87" t="n">
         <v>0.005079693070878803</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
+        <v>19.7695</v>
+      </c>
+      <c r="O87" t="n">
         <v>2.881650614345517</v>
-      </c>
-      <c r="M87" t="n">
-        <v>3.88</v>
       </c>
     </row>
     <row r="88">
@@ -4028,25 +4554,31 @@
         <v>0.008546783741185652</v>
       </c>
       <c r="G88" t="n">
+        <v>16.17904761904762</v>
+      </c>
+      <c r="H88" t="n">
         <v>1.369777006530277</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J88" t="n">
         <v>-0.0228850367140998</v>
       </c>
-      <c r="I88" t="n">
+      <c r="K88" t="n">
         <v>0.01578513089879502</v>
       </c>
-      <c r="J88" t="n">
+      <c r="L88" t="n">
         <v>0.01331134463823958</v>
       </c>
-      <c r="K88" t="n">
+      <c r="M88" t="n">
         <v>0.01092921516824441</v>
       </c>
-      <c r="L88" t="n">
+      <c r="N88" t="n">
+        <v>15.54818181818182</v>
+      </c>
+      <c r="O88" t="n">
         <v>1.245363348637604</v>
-      </c>
-      <c r="M88" t="n">
-        <v>3.72</v>
       </c>
     </row>
     <row r="89">
@@ -4069,25 +4601,31 @@
         <v>0.004001723051714244</v>
       </c>
       <c r="G89" t="n">
+        <v>19.207</v>
+      </c>
+      <c r="H89" t="n">
         <v>1.507539298606209</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J89" t="n">
         <v>0.1366663520095512</v>
       </c>
-      <c r="I89" t="n">
+      <c r="K89" t="n">
         <v>0.017827064221987</v>
       </c>
-      <c r="J89" t="n">
+      <c r="L89" t="n">
         <v>-0.03526161857247523</v>
       </c>
-      <c r="K89" t="n">
+      <c r="M89" t="n">
         <v>0.008546783741185652</v>
       </c>
-      <c r="L89" t="n">
+      <c r="N89" t="n">
+        <v>16.17904761904762</v>
+      </c>
+      <c r="O89" t="n">
         <v>1.369777006530277</v>
-      </c>
-      <c r="M89" t="n">
-        <v>3.64</v>
       </c>
     </row>
   </sheetData>
